--- a/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du dîner. Amandine s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a aussi un concombre vert. Le concombre est froid. Il sent l'eau du jardin. Maman sourit. Maman dit : tu peux goûter. Juste une petite portion. Une petite bouchée. Amandine prend un tout petit morceau. Elle le met dans sa bouche. C'est frais. C'est un peu croquant. Amandine dit : c'est frais, maman. Elle a su nommer le goût. Maman dit : merci d'avoir goûté. Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.</t>
+          <t>C'est l'heure du dîner. Amandine s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a aussi un concombre vert. Le concombre est froid. Il sent l'eau du jardin. Maman sourit. Tu peux goûter. Juste une petite portion. Une petite bouchée. Amandine prend un tout petit morceau. Elle le met dans sa bouche. C'est frais. C'est un peu croquant. C'est frais, maman. Elle a su nommer le goût. Merci d'avoir goûté. Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure du dîner. Amandine s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a aussi un concombre vert. Le concombre est froid. Il sent l'eau du jardin. Maman sourit.
+maman|Tu peux goûter. Juste une petite portion.
+narrateur|Une petite bouchée. Amandine prend un tout petit morceau. Elle le met dans sa bouche. C'est frais. C'est un peu croquant.
+enfant-f|C'est frais, maman. Elle a su nommer le goût.
+maman|Merci d'avoir goûté.
+narrateur|Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine goûte le concombre. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine a goûté. Elle a nommé le goût. Une petite portion, c'est assez. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine boit une gorgée d'eau. Le concombre reste à sa place.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Amandine goûte le concombre. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Amandine a goûté. Elle a nommé le goût. Une petite portion, c'est assez. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Amandine boit une gorgée d'eau. Le concombre reste à sa place.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le concombre d'Amandine</t>
+          <t>Le concombre froid</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le frigo ronronne. Un concombre vert attend sur le linge. Nina le trouve froid comme l'eau. Elle s'assoit. Elle goûte une petite bouchée croquante.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure du dîner. Amandine s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a aussi un concombre vert. Le concombre est froid. Il sent l'eau du jardin. Maman sourit. Tu peux goûter. Juste une petite portion. Une petite bouchée. Amandine prend un tout petit morceau. Elle le met dans sa bouche. C'est frais. C'est un peu croquant. C'est frais, maman. Elle a su nommer le goût. Merci d'avoir goûté. Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.</t>
+          <t>Le frigo fait un petit ronron. Nina colle l'oreille dessus. C'est doux, ce bruit. Dehors, un grillon chante. Le soir arrive sur le village. Nina vit ici, avec maman. Papa ferme les volets, tout près. Le carrelage est encore un peu tiède. Une nappe rayée attend sur la table. Maman ouvre le frigo. Un air froid sort. Nina lève les mains. C'est froid, maman ! Oui. Le frigo garde le frais. Maman pose un concombre sur le linge. Il est long. Il est vert. Il brille un peu. On dirait un crocodile ! Un crocodile très calme. Viens t'asseoir. Nina va vers sa chaise. Elle tire un peu la chaise. Elle s'assoit près de maman. Elle pose les pieds par terre. Bravo, Nina. Tu es bien assise. On est ensemble, à table. Sa chaise ne bouge plus. Dans l'assiette, du riz. Le riz fume un tout petit peu. Tu as vu la petite fumée ? Elle est toute petite. À côté, un rond de concombre. Le rond a un petit cœur blanc. Tu as vu le petit cœur ? Oui, maman. Nina se penche. Ça sent l'eau du jardin. Ça sent l'eau, hein ? Oui. L'eau. Il a quel goût ? Tu peux goûter. Juste une petite portion. Une petite bouchée. Nina prend un tout petit morceau. Elle le met dans sa bouche. Elle goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1329,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est l'heure du dîner. Amandine s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a aussi un concombre vert. Le concombre est froid. Il sent l'eau du jardin. Maman sourit.
-maman|Tu peux goûter. Juste une petite portion.
-narrateur|Une petite bouchée. Amandine prend un tout petit morceau. Elle le met dans sa bouche. C'est frais. C'est un peu croquant.
-enfant-f|C'est frais, maman. Elle a su nommer le goût.
-maman|Merci d'avoir goûté.
-narrateur|Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le frigo fait un petit ronron.
+narrateur|Nina colle l'oreille dessus.
+narrateur|C'est doux, ce bruit.
+narrateur|Dehors, un grillon chante.
+narrateur|Le soir arrive sur le village.
+narrateur|Nina vit ici, avec maman.
+narrateur|Papa ferme les volets, tout près.
+narrateur|Le carrelage est encore un peu tiède.
+narrateur|Une nappe rayée attend sur la table.
+narrateur|Maman ouvre le frigo.
+narrateur|Un air froid sort.
+narrateur|Nina lève les mains.
+enfant-f|C'est froid, maman !
+maman|Oui.
+maman|Le frigo garde le frais.
+narrateur|Maman pose un concombre sur le linge.
+narrateur|Il est long.
+narrateur|Il est vert.
+narrateur|Il brille un peu.
+enfant-f|On dirait un crocodile !
+maman|Un crocodile très calme.
+maman|Viens t'asseoir.
+narrateur|Nina va vers sa chaise.
+narrateur|Elle tire un peu la chaise.
+narrateur|Elle s'assoit près de maman.
+narrateur|Elle pose les pieds par terre.
+maman|Bravo, Nina.
+maman|Tu es bien assise.
+maman|On est ensemble, à table.
+narrateur|Sa chaise ne bouge plus.
+narrateur|Dans l'assiette, du riz.
+narrateur|Le riz fume un tout petit peu.
+maman|Tu as vu la petite fumée ?
+enfant-f|Elle est toute petite.
+narrateur|À côté, un rond de concombre.
+narrateur|Le rond a un petit cœur blanc.
+maman|Tu as vu le petit cœur ?
+enfant-f|Oui, maman.
+narrateur|Nina se penche.
+narrateur|Ça sent l'eau du jardin.
+maman|Ça sent l'eau, hein ?
+enfant-f|Oui. L'eau.
+enfant-f|Il a quel goût ?
+maman|Tu peux goûter.
+maman|Juste une petite portion.
+maman|Une petite bouchée.
+narrateur|Nina prend un tout petit morceau.
+narrateur|Elle le met dans sa bouche.
+narrateur|Elle goûte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>frigo,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amandine goûte le concombre. Que fait-elle ?</t>
+          <t>Nina goûte le concombre. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Amandine goûte le concombre. Que fait-elle ?</t>
+          <t>narrateur|Nina goûte le concombre.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amandine a goûté. Elle a nommé le goût. Une petite portion, c'est assez. Maman est là.</t>
+          <t>Nina mâche. Ça croque. Elle mâche encore un peu. Elle est toujours assise. C'est frais, maman. C'est un peu croquant. Oui. Frais et croquant. Bravo, Nina. Tu as nommé le goût. C'est du bon travail. Le concombre reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1738,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amandine a goûté. Elle a nommé le goût. Une petite portion, c'est assez. Maman est là.</t>
+          <t>narrateur|Nina mâche.
+narrateur|Ça croque.
+narrateur|Elle mâche encore un peu.
+narrateur|Elle est toujours assise.
+enfant-f|C'est frais, maman.
+enfant-f|C'est un peu croquant.
+maman|Oui. Frais et croquant.
+maman|Bravo, Nina.
+maman|Tu as nommé le goût.
+maman|C'est du bon travail.
+narrateur|Le concombre reste dans l'assiette.
+maman|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amandine boit une gorgée d'eau. Le concombre reste à sa place.</t>
+          <t>Nina reste à table. Tu veux un peu d'eau ? Maman verse une gorgée. L'eau fait un petit bruit. Nina boit. Le concombre reste à sa place. Une petite portion, c'est déjà bien. Merci, maman. Merci, Nina. On reste encore un peu ensemble ? Oui. Nina reste assise. Le grillon chante encore. Tu es encore bien assise. Bravo. Le crocodile vert attend, tout calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,7 +1913,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amandine boit une gorgée d'eau. Le concombre reste à sa place.</t>
+          <t>narrateur|Nina reste à table.
+maman|Tu veux un peu d'eau ?
+narrateur|Maman verse une gorgée.
+narrateur|L'eau fait un petit bruit.
+narrateur|Nina boit.
+narrateur|Le concombre reste à sa place.
+maman|Une petite portion, c'est déjà bien.
+enfant-f|Merci, maman.
+maman|Merci, Nina.
+maman|On reste encore un peu ensemble ?
+enfant-f|Oui.
+narrateur|Nina reste assise.
+narrateur|Le grillon chante encore.
+maman|Tu es encore bien assise.
+maman|Bravo.
+narrateur|Le crocodile vert attend, tout calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai goûté une petite bouchée. C'était frais. Bravo. Tu as fait du bon travail. On était assises, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai goûté une petite bouchée.
+enfant-f|C'était frais.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|On était assises, ensemble.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est l'heure du dîner. Amandine s'assoit près de maman. Dans l'assiette, il y a du riz. Il y a aussi un concombre vert. Le concombre est froid. Il sent l'eau du jardin. Maman sourit. Maman dit : tu peux &lt;emphasis level="moderate"&gt;goûter&lt;/emphasis&gt;. Juste une petite portion. Une petite bouchée. Amandine prend un tout petit morceau. Elle le met dans sa bouche. C'est frais. C'est un peu croquant. Amandine dit : c'est frais, maman. Elle a su nommer le goût. Maman dit : merci d'avoir goûté. Une petite portion, c'est déjà bien. Amandine n'a pas besoin de tout finir. Le concombre reste dans l'assiette.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le frigo fait un petit ronron. Nina colle l'oreille dessus. C'est doux, ce bruit. Dehors, un grillon chante. Le soir arrive sur le village. Nina vit ici, avec maman. Papa ferme les volets, tout près. Le carrelage est encore un peu tiède. Une nappe rayée attend sur la table. Maman ouvre le frigo. Un air froid sort. Nina lève les mains. C'est froid, maman ! Oui. Le frigo garde le frais. Maman pose un concombre sur le linge. Il est long. Il est vert. Il brille un peu. On dirait un crocodile ! Un crocodile très calme. Viens t'asseoir. Nina va vers sa chaise. Elle tire un peu la chaise. Elle s'assoit près de maman. Elle pose les pieds par terre. Bravo, Nina. Tu es bien assise. On est ensemble, à table. Sa chaise ne bouge plus. Dans l'assiette, du riz. Le riz fume un tout petit peu. Tu as vu la petite fumée ? Elle est toute petite. À côté, un rond de concombre. Le rond a un petit cœur blanc. Tu as vu le petit cœur ? Oui, maman. Nina se penche. Ça sent l'eau du jardin. Ça sent l'eau, hein ? Oui. L'eau. Il a quel goût ? Tu peux goûter. Juste une petite portion. Une petite bouchée. Nina prend un tout petit morceau. Elle le met dans sa bouche. Elle goûte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amandine goûte le concombre. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina goûte le concombre. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1569,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina mâche. Ça croque. Elle mâche encore un peu. Elle est toujours assise. C'est frais, maman. C'est un peu croquant. Oui. Frais et croquant. Bravo, Nina. Tu as nommé le goût. C'est du bon travail. Le concombre reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
+          <t>Nina mâche. Ça croque. Elle mâche encore un peu. Elle est toujours assise. C'est frais, maman. C'est un peu croquant. Oui. Frais et croquant. Bravo, Nina. Tu as nommé le goût. Le concombre reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amandine a goûté. Elle a nommé le goût. Une &lt;emphasis level="moderate"&gt;petite&lt;/emphasis&gt; portion, c'est assez. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina mâche. Ça croque. Elle mâche encore un peu. Elle est toujours assise. C'est frais, maman. C'est un peu croquant. Oui. Frais et croquant. Bravo, Nina. Tu as nommé le goût. Le concombre reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,12 +1746,10 @@
 maman|Oui. Frais et croquant.
 maman|Bravo, Nina.
 maman|Tu as nommé le goût.
-maman|C'est du bon travail.
 narrateur|Le concombre reste dans l'assiette.
 maman|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amandine boit une gorgée d'eau. Le concombre reste à sa place.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina reste à table. Tu veux un peu d'eau ? Maman verse une gorgée. L'eau fait un petit bruit. Nina boit. Le concombre reste à sa place. Une petite portion, c'est déjà bien. Merci, maman. Merci, Nina. On reste encore un peu ensemble ? Oui. Nina reste assise. Le grillon chante encore. Tu es encore bien assise. Bravo. Le crocodile vert attend, tout calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1928,6 @@
 narrateur|Le crocodile vert attend, tout calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai goûté une petite bouchée. C'était frais. Bravo. Tu as fait du bon travail. On était assises, ensemble. L'histoire est finie.</t>
+          <t>J'ai goûté une petite bouchée. C'était frais. Bravo. On était assises, ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai goûté une petite bouchée. C'était frais. Bravo. On était assises, ensemble.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2095,9 @@
           <t>enfant-f|J'ai goûté une petite bouchée.
 enfant-f|C'était frais.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|On était assises, ensemble.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|On était assises, ensemble.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-07.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amandine, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
